--- a/arquivos/arquivo_modelo.xlsx
+++ b/arquivos/arquivo_modelo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47301966-7786-4313-B5CA-7DE7DE7944CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF15C7C5-8D6E-4949-B24D-E63CECC0EF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
     <t>GIGA+</t>
   </si>
   <si>
-    <t>AMERICA NET</t>
+    <t>VERO</t>
   </si>
 </sst>
 </file>

--- a/arquivos/arquivo_modelo.xlsx
+++ b/arquivos/arquivo_modelo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF15C7C5-8D6E-4949-B24D-E63CECC0EF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F2F568-A593-4707-A025-FC6A7563572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>SEV</t>
   </si>
@@ -73,6 +73,21 @@
   </si>
   <si>
     <t>VERO</t>
+  </si>
+  <si>
+    <t>BRFIBRA</t>
+  </si>
+  <si>
+    <t>BRSULNET</t>
+  </si>
+  <si>
+    <t>SEBRATEL</t>
+  </si>
+  <si>
+    <t>TELLIUS</t>
+  </si>
+  <si>
+    <t>ATIVA TELECOM-MG</t>
   </si>
 </sst>
 </file>
@@ -390,24 +405,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.109375" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,9 +475,24 @@
         <v>15</v>
       </c>
       <c r="O1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" t="s">
         <v>4</v>
       </c>
-      <c r="P1" t="s">
+      <c r="U1" t="s">
         <v>5</v>
       </c>
     </row>
